--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="14115" windowHeight="8745"/>
   </bookViews>
   <sheets>
     <sheet name="平台库存差异" sheetId="1" r:id="rId1"/>
@@ -27,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>核对周期</t>
   </si>
   <si>
+    <t>核对仓库</t>
+  </si>
+  <si>
     <t>ERP_SKU</t>
   </si>
   <si>
@@ -72,6 +75,9 @@
   </si>
   <si>
     <t>{.checkMonth}</t>
+  </si>
+  <si>
+    <t>{.warehouseName}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -1300,13 +1306,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="14" width="30" customWidth="1"/>
+    <col min="1" max="15" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:14">
+    <row r="1" ht="15" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1349,49 +1355,55 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14115" windowHeight="8745"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="平台库存差异" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>核对周期</t>
   </si>
@@ -53,10 +53,16 @@
     <t>本月期末(计算)</t>
   </si>
   <si>
-    <t>本月期末(每日来源)</t>
-  </si>
-  <si>
-    <t>平台本月期末</t>
+    <t>本月期末(每日来源)(在库)</t>
+  </si>
+  <si>
+    <t>本月期末(每日来源)(在途)</t>
+  </si>
+  <si>
+    <t>平台本月期末（在库）</t>
+  </si>
+  <si>
+    <t>平台本月期末（在途）</t>
   </si>
   <si>
     <t xml:space="preserve">差异数量 </t>
@@ -101,7 +107,13 @@
     <t>{.estimatedClosingQty}</t>
   </si>
   <si>
+    <t>{.intransitQty}</t>
+  </si>
+  <si>
     <t>{.platformClosingQty}</t>
+  </si>
+  <si>
+    <t>{.platformClosingIntransitQty}</t>
   </si>
   <si>
     <t>{.diffClosingQty}</t>
@@ -1306,13 +1318,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="15" width="30" customWidth="1"/>
+    <col min="1" max="17" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:15">
+    <row r="1" ht="15" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1358,52 +1370,64 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiff.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>核对周期</t>
   </si>
@@ -65,7 +65,10 @@
     <t>平台本月期末（在途）</t>
   </si>
   <si>
-    <t xml:space="preserve">差异数量 </t>
+    <t>差异数量（在库）</t>
+  </si>
+  <si>
+    <t>差异数量（在途）</t>
   </si>
   <si>
     <t>备注</t>
@@ -117,6 +120,9 @@
   </si>
   <si>
     <t>{.diffClosingQty}</t>
+  </si>
+  <si>
+    <t>{.diffClosingIntransitQty}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1318,13 +1324,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="17" width="30" customWidth="1"/>
+    <col min="1" max="18" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:17">
+    <row r="1" ht="15" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1376,58 +1382,64 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiff.xlsx
@@ -104,10 +104,10 @@
     <t>{.instockQty}</t>
   </si>
   <si>
+    <t>{.estimatedClosingQty}</t>
+  </si>
+  <si>
     <t>{.closingQty}</t>
-  </si>
-  <si>
-    <t>{.estimatedClosingQty}</t>
   </si>
   <si>
     <t>{.intransitQty}</t>
